--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-24 13:41</t>
+          <t>更新时间: 2026-09-25 13:39</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-25 13:39</t>
+          <t>更新时间: 2026-09-26 13:44</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-26 13:44</t>
+          <t>更新时间: 2026-09-27 14:02</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-27 14:02</t>
+          <t>更新时间: 2026-09-28 14:09</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-28 14:09</t>
+          <t>更新时间: 2026-09-29 14:26</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-29 14:26</t>
+          <t>更新时间: 2026-09-30 14:12</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-30 14:12</t>
+          <t>更新时间: 2026-10-01 14:42</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-01 14:42</t>
+          <t>更新时间: 2026-10-02 14:29</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-02 14:29</t>
+          <t>更新时间: 2026-10-03 13:56</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-03 13:56</t>
+          <t>更新时间: 2026-10-04 14:34</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-04 14:34</t>
+          <t>更新时间: 2026-10-05 14:28</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-05 14:28</t>
+          <t>更新时间: 2026-10-06 15:02</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-06 15:02</t>
+          <t>更新时间: 2026-10-07 14:44</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-07 14:44</t>
+          <t>更新时间: 2026-10-08 14:53</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-08 14:53</t>
+          <t>更新时间: 2026-10-09 15:01</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-09 15:01</t>
+          <t>更新时间: 2026-10-10 14:33</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-27 13:49</t>
+          <t>更新时间: 2026-10-28 14:28</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-28 14:28</t>
+          <t>更新时间: 2026-10-29 14:39</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-29 14:39</t>
+          <t>更新时间: 2026-10-30 14:40</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-30 14:40</t>
+          <t>更新时间: 2026-10-31 14:30</t>
         </is>
       </c>
     </row>
